--- a/xy10102/output/statistics.xlsx
+++ b/xy10102/output/statistics.xlsx
@@ -470,7 +470,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>57.35602641717116</v>
+        <v>57.27288245219347</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -478,7 +478,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>40.1914777028644</v>
+        <v>40.24812635436002</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>51.495</v>
+        <v>51.355</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -510,7 +510,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>29.05242157402311</v>
+        <v>29.02799775028122</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -518,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>23.36547870642356</v>
+        <v>23.38708735136345</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -542,7 +542,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>23.82</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -550,7 +550,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>30.81928453494772</v>
+        <v>30.82930539932509</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -558,7 +558,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>9.5644469497974</v>
+        <v>9.563842741510451</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -590,7 +590,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.8140200880572372</v>
+        <v>0.813369235095613</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -598,7 +598,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.3040877670822433</v>
+        <v>0.3042099385181197</v>
       </c>
     </row>
     <row r="20" spans="1:2">
